--- a/ExyteDynamo/equ_room_data.xlsx
+++ b/ExyteDynamo/equ_room_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ychiang2\Desktop\20250513\ExyteHelloWorld\ExyteDynamo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B567AEF-071C-4C39-9EFD-A4E4A4D7F60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF33963-4454-47D9-919A-E8F2A445C23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2170" windowWidth="14400" windowHeight="8750" xr2:uid="{BA1F1ACE-F086-4C3D-90CC-56D3466A2A49}"/>
+    <workbookView xWindow="0" yWindow="2650" windowWidth="19380" windowHeight="8870" xr2:uid="{DB2031A3-C00D-428F-9450-99F88819C808}"/>
   </bookViews>
   <sheets>
     <sheet name="data1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="23">
   <si>
     <t>Family Type: 14 kW, Family: M_WSHP - Horizontal - High Efficiency - 7-18 kW - Left Return - Right Discharge</t>
   </si>
@@ -106,21 +106,6 @@
   </si>
   <si>
     <t>Elevator</t>
-  </si>
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
-  </si>
-  <si>
-    <t>Column4</t>
-  </si>
-  <si>
-    <t>Column5</t>
   </si>
 </sst>
 </file>
@@ -172,20 +157,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B37BD251-9F69-4C3A-BD8E-6714A9FBFE13}" name="Table1" displayName="Table1" ref="A1:E48" totalsRowShown="0">
-  <autoFilter ref="A1:E48" xr:uid="{B37BD251-9F69-4C3A-BD8E-6714A9FBFE13}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1F093E02-46D8-4054-BE14-FFC9B5E76F0A}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{26E1248D-B2E4-4464-B754-A061F18578FB}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{875248ED-D8FA-4DEA-BEEE-80B85ADDBC0F}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{7311AD45-A684-40FB-A8B3-072E79025B0A}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{540FB72E-7E9B-4C8D-A65B-0143EB44F261}" name="Column5"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -504,29 +475,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2013375-B282-4E8F-8964-C08425DA034E}">
-  <dimension ref="A1:E48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABC4F41-4FB1-4A83-A623-3577AD9B3A20}">
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="95.90625" customWidth="1"/>
-    <col min="2" max="5" width="10.26953125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -548,7 +515,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -565,7 +532,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -582,7 +549,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -599,7 +566,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -616,7 +583,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -684,7 +651,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
@@ -701,7 +668,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -718,19 +685,19 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -752,7 +719,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -786,7 +753,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -803,7 +770,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -871,7 +838,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -888,7 +855,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -905,41 +872,41 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -981,38 +948,38 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E29">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B31" t="s">
         <v>16</v>
@@ -1063,7 +1030,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
@@ -1080,7 +1047,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
@@ -1097,7 +1064,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
@@ -1114,7 +1081,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
@@ -1165,7 +1132,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
@@ -1182,7 +1149,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
@@ -1199,7 +1166,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
@@ -1216,92 +1183,72 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>14</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E46">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E47">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>20</v>
-      </c>
-      <c r="B48" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{338ABCB1-2370-486B-9A65-B5ED0C3D3777}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB03CD39-AC7F-4AA3-8ACD-24F7302D23AE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData/>
